--- a/data/proc_data/private_data/2025_a_conectividad.xlsx
+++ b/data/proc_data/private_data/2025_a_conectividad.xlsx
@@ -357,182 +357,182 @@
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>number</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Comuna</t>
+          <t>comuna</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Código_comuna</t>
+          <t>codigo_comuna</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Región</t>
+          <t>region</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Código_comuna_n</t>
+          <t>codigo_comuna_n</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Código_región</t>
+          <t>codigo_region</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>IDC_2024</t>
+          <t>idc_2024</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Población_censo_2024</t>
+          <t>poblacion_censo_2024</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Conexiones_fijas_residenciales_2024</t>
+          <t>conexiones_fijas_residenciales_2024</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>ADSL_tecnología_2024</t>
+          <t>adsl_tecnologia_2024</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>FTTX_tecnología_2024</t>
+          <t>fttx_tecnologia_2024</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>MODEM_tecnología_2024</t>
+          <t>modem_tecnologia_2024</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>OTA_tecnología_2024</t>
+          <t>ota_tecnologia_2024</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>OTI_tecnología_2024</t>
+          <t>oti_tecnologia_2024</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>W_tecnología_2024</t>
+          <t>w_tecnologia_2024</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Conectividad_2025_bruto</t>
+          <t>conectividad_2025_bruto</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Conectividad_2025_bruto_3</t>
+          <t>conectividad_2025_bruto_3</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Conectividad_2025_estandarizada</t>
+          <t>conectividad_2025_estandarizada</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Conectividad_2025_estandarizada_3</t>
+          <t>conectividad_2025_estandarizada_3</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Posición_dimensión_2025</t>
+          <t>posicion_dimension_2025</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Población_proyección_2023_base2017</t>
+          <t>poblacion_proyeccion_2023_base2017</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Conexiones_fijas_residenciales_2023</t>
+          <t>conexiones_fijas_residenciales_2023</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>ADSL_tecnología_2023</t>
+          <t>adsl_tecnologia_2023</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>FTTX_tecnología_2023</t>
+          <t>fttx_tecnologia_2023</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>MODEM_tecnología_2023</t>
+          <t>modem_tecnologia_2023</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>OTA_tecnología_2023</t>
+          <t>ota_tecnologia_2023</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>OTI_tecnología_2023</t>
+          <t>oti_tecnologia_2023</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>W_tecnología_2023</t>
+          <t>w_tecnologia_2023</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>Conectividad_2024_bruto</t>
+          <t>conectividad_2024_bruto</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>Conectividad_2024_bruto_3</t>
+          <t>conectividad_2024_bruto_3</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>Conectividad_2024_estandarizada</t>
+          <t>conectividad_2024_estandarizada</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>Conectividad_2024_estandarizada_3</t>
+          <t>conectividad_2024_estandarizada_3</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>Posición_dimensión_2024</t>
+          <t>posicion_dimension_2024</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>C25V</t>
+          <t>c25v</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>C25V_z</t>
+          <t>c25v_z</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>C25V_z_3</t>
+          <t>c25v_z_3</t>
         </is>
       </c>
     </row>
